--- a/api/templates/mtb_detected_rr_detected/es.xlsx
+++ b/api/templates/mtb_detected_rr_detected/es.xlsx
@@ -1,34 +1,34 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <workbookPr date1904="0"/>
-  <workbookProtection/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <bookViews>
     <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="Results" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet sheetId="1" name="Results" state="visible" r:id="rId4"/>
   </sheets>
-  <calcPr refMode="A1" iterate="0" iterateCount="100" iterateDelta="0.0001"/>
+  <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="36">
-  <si>
-    <t xml:space="preserve">MTB Detectado, RR Detectado</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Entre fechas: &lt;Dates&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Estados: &lt;States&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ciudades: &lt;Lgas&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sitios: &lt;Sites&gt;</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="38">
+  <si>
+    <t>MTB Detectado, RR Detectado</t>
+  </si>
+  <si>
+    <t>Entre fechas: &lt;Dates&gt;</t>
+  </si>
+  <si>
+    <t>Estados: &lt;States&gt;</t>
+  </si>
+  <si>
+    <t>Ciudades: &lt;Lgas&gt;</t>
+  </si>
+  <si>
+    <t>Sitios: &lt;Sites&gt;</t>
   </si>
   <si>
     <t>&lt;Table&gt;</t>
@@ -37,16 +37,16 @@
     <t>#</t>
   </si>
   <si>
-    <t xml:space="preserve">ID Paciente</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ID Paciente 2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Id de caso</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ID de muestra</t>
+    <t>ID Paciente</t>
+  </si>
+  <si>
+    <t>ID Paciente 2</t>
+  </si>
+  <si>
+    <t>Id de caso</t>
+  </si>
+  <si>
+    <t>ID de muestra</t>
   </si>
   <si>
     <t>Edad</t>
@@ -55,13 +55,16 @@
     <t>Dispositivo</t>
   </si>
   <si>
-    <t xml:space="preserve">Identificador de Dispositivo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fecha del test</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nombre del ensayo</t>
+    <t>Sitio</t>
+  </si>
+  <si>
+    <t>Identificador de Dispositivo</t>
+  </si>
+  <si>
+    <t>Fecha del test</t>
+  </si>
+  <si>
+    <t>Nombre del ensayo</t>
   </si>
   <si>
     <t>MTB</t>
@@ -70,13 +73,13 @@
     <t>RIF</t>
   </si>
   <si>
-    <t xml:space="preserve">Resultado del test</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Código de error</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Notas del test</t>
+    <t>Resultado del test</t>
+  </si>
+  <si>
+    <t>Código de error</t>
+  </si>
+  <si>
+    <t>Notas del test</t>
   </si>
   <si>
     <t>&lt;#&gt;</t>
@@ -98,6 +101,9 @@
   </si>
   <si>
     <t>&lt;deviceName&gt;</t>
+  </si>
+  <si>
+    <t>&lt;siteName&gt;</t>
   </si>
   <si>
     <t>&lt;instrumentSerial&gt;</t>
@@ -127,32 +133,35 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="dd\-mm\-yyyy;@"/>
+    <numFmt numFmtId="164" formatCode="dd-mm-yyyy;@"/>
   </numFmts>
-  <fonts count="5">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
-      <sz val="11.000000"/>
       <color theme="1"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+      <sz val="11"/>
       <name val="Calibri"/>
     </font>
     <font>
-      <sz val="10.000000"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="12.000000"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <name val="Calibri"/>
     </font>
     <font>
       <b/>
-      <sz val="16.000000"/>
+      <sz val="16"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="12"/>
       <name val="Calibri"/>
     </font>
     <font>
       <b/>
-      <sz val="12.000000"/>
+      <sz val="12"/>
       <name val="Calibri"/>
     </font>
   </fonts>
@@ -170,7 +179,14 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="11">
+  <borders count="12">
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
     <border>
       <left style="none"/>
       <right style="none"/>
@@ -207,43 +223,37 @@
       <diagonal style="none"/>
     </border>
     <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
+      <left style="medium"/>
+      <right style="medium"/>
+      <top style="medium"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
       <right style="medium">
-        <color auto="1"/>
+        <color theme="1"/>
       </right>
       <top style="medium">
-        <color auto="1"/>
+        <color theme="1"/>
+      </top>
+      <bottom style="medium">
+        <color theme="1"/>
+      </bottom>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="medium">
+        <color theme="1"/>
+      </right>
+      <top style="medium">
+        <color theme="1"/>
       </top>
       <bottom style="none"/>
       <diagonal style="none"/>
     </border>
     <border>
-      <left style="none"/>
-      <right style="medium">
-        <color theme="1"/>
-      </right>
-      <top style="medium">
-        <color theme="1"/>
-      </top>
-      <bottom style="medium">
-        <color theme="1"/>
-      </bottom>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="medium">
-        <color theme="1"/>
-      </right>
-      <top style="medium">
-        <color theme="1"/>
-      </top>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
       <left style="thin">
         <color theme="1"/>
       </left>
@@ -272,18 +282,10 @@
       <diagonal style="none"/>
     </border>
     <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
       <diagonal style="none"/>
     </border>
     <border>
@@ -311,96 +313,55 @@
       <diagonal style="none"/>
     </border>
   </borders>
-  <cellStyleXfs count="7">
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
-      <protection hidden="0" locked="1"/>
-    </xf>
-    <xf fontId="1" fillId="0" borderId="0" numFmtId="43" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyProtection="0"/>
-    <xf fontId="1" fillId="0" borderId="0" numFmtId="41" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyProtection="0"/>
-    <xf fontId="1" fillId="0" borderId="0" numFmtId="44" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyProtection="0"/>
-    <xf fontId="1" fillId="0" borderId="0" numFmtId="42" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyProtection="0"/>
-    <xf fontId="1" fillId="0" borderId="0" numFmtId="9" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyProtection="0"/>
-    <xf fontId="2" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="0"/>
+  <cellStyleXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="21">
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyProtection="0">
-      <protection hidden="0" locked="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-      <protection hidden="0" locked="1"/>
     </xf>
-    <xf fontId="3" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyProtection="1">
-      <protection hidden="0" locked="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf fontId="3" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-      <protection hidden="0" locked="1"/>
     </xf>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyProtection="1">
-      <protection hidden="0" locked="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf fontId="2" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyProtection="1">
-      <protection hidden="0" locked="1"/>
-    </xf>
-    <xf fontId="2" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection hidden="0" locked="1"/>
-    </xf>
-    <xf fontId="2" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection hidden="0" locked="1"/>
-    </xf>
-    <xf fontId="4" fillId="2" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection hidden="0" locked="1"/>
-    </xf>
-    <xf fontId="4" fillId="2" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
-      <protection hidden="0" locked="1"/>
-    </xf>
-    <xf fontId="4" fillId="2" borderId="2" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
-      <protection hidden="0" locked="1"/>
-    </xf>
-    <xf fontId="4" fillId="2" borderId="3" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1"/>
-    <xf fontId="4" fillId="2" borderId="4" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
-      <protection hidden="0" locked="1"/>
-    </xf>
-    <xf fontId="4" fillId="2" borderId="5" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
-      <protection hidden="0" locked="1"/>
-    </xf>
-    <xf fontId="2" fillId="0" borderId="6" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection hidden="0" locked="1"/>
-    </xf>
-    <xf fontId="2" fillId="0" borderId="6" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
-      <protection hidden="0" locked="1"/>
-    </xf>
-    <xf fontId="2" fillId="0" borderId="7" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
-      <protection hidden="0" locked="1"/>
-    </xf>
-    <xf fontId="2" fillId="0" borderId="8" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyProtection="1"/>
-    <xf fontId="2" fillId="0" borderId="9" numFmtId="164" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyProtection="1">
-      <protection hidden="0" locked="1"/>
-    </xf>
-    <xf fontId="2" fillId="0" borderId="8" numFmtId="164" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyProtection="1"/>
-    <xf fontId="2" fillId="0" borderId="10" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
-      <protection hidden="0" locked="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
-  <cellStyles count="7">
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Comma" xfId="1" builtinId="3"/>
-    <cellStyle name="Comma [0]" xfId="2" builtinId="6"/>
-    <cellStyle name="Currency" xfId="3" builtinId="4"/>
-    <cellStyle name="Currency [0]" xfId="4" builtinId="7"/>
-    <cellStyle name="Percent" xfId="5" builtinId="5"/>
-    <cellStyle name="Normal 2" xfId="6"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -861,25 +822,27 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
-  <sheetPr filterMode="0">
-    <outlinePr applyStyles="0" summaryBelow="1" summaryRight="1" showOutlineSymbols="1"/>
-    <pageSetUpPr autoPageBreaks="1" fitToPage="0"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <sheetFormatPr defaultColWidth="8.68359375" defaultRowHeight="14.25"/>
+  <dimension ref="A1:P11"/>
+  <sheetFormatPr defaultRowHeight="14.25" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="8.68359375" customHeight="1"/>
   <cols>
-    <col customWidth="1" min="1" max="1" style="0" width="7.5300000000000002"/>
-    <col customWidth="1" min="2" max="4" style="0" width="24.23"/>
-    <col customWidth="1" min="5" max="5" style="0" width="23.149999999999999"/>
-    <col customWidth="1" min="6" max="6" style="1" width="15.84"/>
-    <col customWidth="1" min="7" max="8" style="0" width="28"/>
-    <col customWidth="1" min="9" max="10" style="0" width="18.539999999999999"/>
-    <col customWidth="1" min="11" max="11" style="0" width="14.460000000000001"/>
-    <col customWidth="1" min="12" max="14" style="0" width="16.68"/>
-    <col customWidth="1" min="15" max="15" style="0" width="60.689999999999998"/>
+    <col min="1" max="1" width="7.53" customWidth="1"/>
+    <col min="2" max="4" width="24.23" customWidth="1"/>
+    <col min="5" max="5" width="23.15" customWidth="1"/>
+    <col min="6" max="6" width="15.84" style="1" customWidth="1"/>
+    <col min="7" max="7" width="28" customWidth="1"/>
+    <col min="8" max="8" width="25" customWidth="1"/>
+    <col min="9" max="9" width="28" customWidth="1"/>
+    <col min="10" max="11" width="18.54" customWidth="1"/>
+    <col min="12" max="12" width="14.46" customWidth="1"/>
+    <col min="13" max="15" width="16.68" customWidth="1"/>
+    <col min="16" max="16" width="60.69" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="21">
+    <row r="1" ht="21" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -898,7 +861,7 @@
       <c r="N1" s="2"/>
       <c r="O1" s="2"/>
     </row>
-    <row r="2" ht="16.5">
+    <row r="2" ht="16.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
         <v>1</v>
       </c>
@@ -917,7 +880,7 @@
       <c r="N2" s="5"/>
       <c r="O2" s="5"/>
     </row>
-    <row r="3" ht="16.5">
+    <row r="3" ht="16.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
         <v>2</v>
       </c>
@@ -936,7 +899,7 @@
       <c r="N3" s="5"/>
       <c r="O3" s="5"/>
     </row>
-    <row r="4" ht="16.5">
+    <row r="4" ht="16.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
         <v>3</v>
       </c>
@@ -955,7 +918,7 @@
       <c r="N4" s="5"/>
       <c r="O4" s="5"/>
     </row>
-    <row r="5" ht="16.5">
+    <row r="5" ht="16.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
         <v>4</v>
       </c>
@@ -974,7 +937,7 @@
       <c r="N5" s="5"/>
       <c r="O5" s="5"/>
     </row>
-    <row r="6" ht="16.5">
+    <row r="6" ht="16.5" customHeight="1" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B6" s="5"/>
       <c r="C6" s="5"/>
       <c r="D6" s="5"/>
@@ -990,7 +953,7 @@
       <c r="N6" s="5"/>
       <c r="O6" s="5"/>
     </row>
-    <row r="7" ht="16.5">
+    <row r="7" ht="16.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="s">
         <v>5</v>
       </c>
@@ -1011,7 +974,7 @@
       <c r="N7" s="5"/>
       <c r="O7" s="6"/>
     </row>
-    <row r="8" ht="31" customHeight="1">
+    <row r="8" ht="31" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A8" s="8" t="s">
         <v>6</v>
       </c>
@@ -1033,16 +996,16 @@
       <c r="G8" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="H8" s="11" t="s">
+      <c r="H8" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="I8" s="12" t="s">
+      <c r="I8" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="J8" s="13" t="s">
+      <c r="J8" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="K8" s="9" t="s">
+      <c r="K8" s="13" t="s">
         <v>16</v>
       </c>
       <c r="L8" s="9" t="s">
@@ -1057,58 +1020,64 @@
       <c r="O8" s="9" t="s">
         <v>20</v>
       </c>
+      <c r="P8" s="9" t="s">
+        <v>21</v>
+      </c>
     </row>
-    <row r="9" ht="16.5">
+    <row r="9" ht="16.5" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A9" s="14" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B9" s="15" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C9" s="15" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D9" s="15" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E9" s="15" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F9" s="14" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G9" s="16" t="s">
-        <v>27</v>
-      </c>
-      <c r="H9" s="17" t="s">
         <v>28</v>
       </c>
-      <c r="I9" s="18" t="s">
+      <c r="H9" s="16" t="s">
         <v>29</v>
       </c>
-      <c r="J9" s="19" t="s">
+      <c r="I9" s="17" t="s">
         <v>30</v>
       </c>
-      <c r="K9" s="20" t="s">
+      <c r="J9" s="18" t="s">
         <v>31</v>
       </c>
-      <c r="L9" s="15" t="s">
+      <c r="K9" s="19" t="s">
         <v>32</v>
       </c>
+      <c r="L9" s="20" t="s">
+        <v>33</v>
+      </c>
       <c r="M9" s="15" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="N9" s="15" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="O9" s="15" t="s">
-        <v>35</v>
+        <v>36</v>
+      </c>
+      <c r="P9" s="15" t="s">
+        <v>37</v>
       </c>
     </row>
+    <row r="10" spans="8:16" x14ac:dyDescent="0.25"/>
+    <row r="11" spans="8:16" x14ac:dyDescent="0.25"/>
   </sheetData>
-  <printOptions headings="0" gridLines="0" horizontalCentered="0" verticalCentered="0"/>
-  <pageMargins left="0.69999999999999996" right="0.69999999999999996" top="0.75" bottom="0.75" header="0.51181102362204689" footer="0.51181102362204689"/>
-  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.5118110236220469" footer="0.5118110236220469"/>
+  <pageSetup paperSize="1" orientation="portrait" horizontalDpi="300" verticalDpi="300" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" usePrinterDefaults="1" copies="1"/>
 </worksheet>
 </file>